--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\新卡台清洗仓库\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C57CCD-9085-4A73-973B-BA5D99F12ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBE426B-2073-4B47-A775-8A86F250B917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="95">
   <si>
     <t>UA名字</t>
   </si>
@@ -302,6 +302,16 @@
   </si>
   <si>
     <t>6946</t>
+  </si>
+  <si>
+    <t>4903</t>
+  </si>
+  <si>
+    <t>0258</t>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -673,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1097,18 +1107,18 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1116,7 +1126,7 @@
         <v>47</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1124,7 +1134,7 @@
         <v>47</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1132,7 +1142,7 @@
         <v>47</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1140,7 +1150,7 @@
         <v>47</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -1148,7 +1158,7 @@
         <v>47</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -1156,7 +1166,7 @@
         <v>47</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -1164,23 +1174,23 @@
         <v>47</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -1188,7 +1198,7 @@
         <v>55</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -1196,7 +1206,7 @@
         <v>55</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -1204,7 +1214,7 @@
         <v>55</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -1212,23 +1222,23 @@
         <v>55</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -1236,7 +1246,7 @@
         <v>62</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -1244,7 +1254,7 @@
         <v>62</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -1252,7 +1262,7 @@
         <v>62</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -1260,7 +1270,7 @@
         <v>62</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -1268,7 +1278,7 @@
         <v>62</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -1276,7 +1286,7 @@
         <v>62</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -1284,39 +1294,39 @@
         <v>62</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B79" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B80" s="4" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -1324,7 +1334,7 @@
         <v>70</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -1332,7 +1342,48 @@
         <v>70</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBE426B-2073-4B47-A775-8A86F250B917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD02AA8-0CD7-42A9-8B7D-A121333FE242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="94">
   <si>
     <t>UA名字</t>
   </si>
@@ -308,10 +308,6 @@
   </si>
   <si>
     <t>0258</t>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -683,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1361,31 +1357,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B85" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B86" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B87" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B88" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B89" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD02AA8-0CD7-42A9-8B7D-A121333FE242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEC8692-2FBF-41CC-A5C0-11478E6B68DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="105">
   <si>
     <t>UA名字</t>
   </si>
@@ -193,9 +202,6 @@
     <t>5850</t>
   </si>
   <si>
-    <t>yves</t>
-  </si>
-  <si>
     <t>5852</t>
   </si>
   <si>
@@ -308,13 +314,49 @@
   </si>
   <si>
     <t>0258</t>
+  </si>
+  <si>
+    <t>7385</t>
+  </si>
+  <si>
+    <t>3831</t>
+  </si>
+  <si>
+    <t>1965</t>
+  </si>
+  <si>
+    <t>8909</t>
+  </si>
+  <si>
+    <t>3157</t>
+  </si>
+  <si>
+    <t>wzq</t>
+  </si>
+  <si>
+    <t>sevan</t>
+  </si>
+  <si>
+    <t>1513</t>
+  </si>
+  <si>
+    <t>1597</t>
+  </si>
+  <si>
+    <t>jz</t>
+  </si>
+  <si>
+    <t>1897</t>
+  </si>
+  <si>
+    <t>5442</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,15 +381,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -387,16 +423,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -679,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -694,667 +727,739 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="A15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="4" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="4" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="4" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="B30" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B31" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B33" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="3" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="B42" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B37" s="3" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B62" s="3" t="s">
+      <c r="B68" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B64" s="3" t="s">
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="3" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B66" s="3" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B67" s="3" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B68" s="3" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B69" s="3" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+      <c r="B75" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B70" s="3" t="s">
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="3" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72" s="3" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B73" s="3" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B74" s="3" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75" s="3" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B77" s="3" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>74</v>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEC8692-2FBF-41CC-A5C0-11478E6B68DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C994D03A-777C-4125-835D-AB35D11C1A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="106">
   <si>
     <t>UA名字</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>5442</t>
+  </si>
+  <si>
+    <t>1286</t>
   </si>
 </sst>
 </file>
@@ -712,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -984,10 +987,10 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -995,7 +998,7 @@
         <v>22</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1003,7 +1006,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1011,7 +1014,7 @@
         <v>22</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1019,7 +1022,7 @@
         <v>22</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1027,7 +1030,7 @@
         <v>22</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1035,7 +1038,7 @@
         <v>22</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1043,7 +1046,7 @@
         <v>22</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1051,15 +1054,15 @@
         <v>22</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1067,7 +1070,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1075,7 +1078,7 @@
         <v>30</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1083,7 +1086,7 @@
         <v>30</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1091,7 +1094,7 @@
         <v>30</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1099,15 +1102,15 @@
         <v>30</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1115,7 +1118,7 @@
         <v>37</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1123,7 +1126,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1131,7 +1134,7 @@
         <v>37</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1139,7 +1142,7 @@
         <v>37</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1147,7 +1150,7 @@
         <v>37</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1155,7 +1158,7 @@
         <v>37</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1163,7 +1166,7 @@
         <v>37</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1171,7 +1174,7 @@
         <v>37</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1179,7 +1182,7 @@
         <v>37</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -1187,15 +1190,15 @@
         <v>37</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -1203,7 +1206,7 @@
         <v>47</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -1211,7 +1214,7 @@
         <v>47</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -1219,7 +1222,7 @@
         <v>47</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -1227,7 +1230,7 @@
         <v>47</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -1235,7 +1238,7 @@
         <v>47</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -1243,7 +1246,7 @@
         <v>47</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -1251,7 +1254,7 @@
         <v>47</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -1259,15 +1262,15 @@
         <v>47</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -1275,7 +1278,7 @@
         <v>98</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -1283,7 +1286,7 @@
         <v>98</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -1291,7 +1294,7 @@
         <v>98</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -1299,7 +1302,7 @@
         <v>98</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -1307,15 +1310,15 @@
         <v>98</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -1323,7 +1326,7 @@
         <v>61</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -1331,7 +1334,7 @@
         <v>61</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -1339,7 +1342,7 @@
         <v>61</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -1347,7 +1350,7 @@
         <v>61</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -1355,7 +1358,7 @@
         <v>61</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -1363,7 +1366,7 @@
         <v>61</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -1371,7 +1374,7 @@
         <v>61</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -1379,15 +1382,15 @@
         <v>61</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -1395,15 +1398,15 @@
         <v>61</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -1411,7 +1414,7 @@
         <v>69</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -1419,7 +1422,7 @@
         <v>69</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -1427,15 +1430,15 @@
         <v>69</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -1443,15 +1446,15 @@
         <v>99</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -1459,6 +1462,14 @@
         <v>102</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>104</v>
       </c>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C994D03A-777C-4125-835D-AB35D11C1A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B907D14-47B0-44CB-9A3D-100800DFA8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="111">
   <si>
     <t>UA名字</t>
   </si>
@@ -220,9 +220,6 @@
     <t>2966</t>
   </si>
   <si>
-    <t>jack</t>
-  </si>
-  <si>
     <t>9148</t>
   </si>
   <si>
@@ -353,6 +350,24 @@
   </si>
   <si>
     <t>1286</t>
+  </si>
+  <si>
+    <t>mhx</t>
+  </si>
+  <si>
+    <t>3119</t>
+  </si>
+  <si>
+    <t>wwl</t>
+  </si>
+  <si>
+    <t>1637</t>
+  </si>
+  <si>
+    <t>qmy</t>
+  </si>
+  <si>
+    <t>2126</t>
   </si>
 </sst>
 </file>
@@ -715,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -838,7 +853,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -846,7 +861,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -854,7 +869,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -862,7 +877,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -870,7 +885,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -878,7 +893,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -886,7 +901,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -894,7 +909,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -902,7 +917,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -910,7 +925,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -958,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -966,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -974,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -982,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -990,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1054,7 +1069,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1062,7 +1077,7 @@
         <v>22</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1190,7 +1205,7 @@
         <v>37</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -1198,7 +1213,7 @@
         <v>37</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -1262,7 +1277,7 @@
         <v>47</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -1270,12 +1285,12 @@
         <v>47</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>55</v>
@@ -1283,7 +1298,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>56</v>
@@ -1291,7 +1306,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>57</v>
@@ -1299,7 +1314,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>58</v>
@@ -1307,7 +1322,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>59</v>
@@ -1315,7 +1330,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>60</v>
@@ -1323,154 +1338,178 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B907D14-47B0-44CB-9A3D-100800DFA8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23CC36F-B4BF-409B-B35F-BD2D71A00FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="110">
   <si>
     <t>UA名字</t>
   </si>
@@ -329,9 +329,6 @@
   </si>
   <si>
     <t>wzq</t>
-  </si>
-  <si>
-    <t>sevan</t>
   </si>
   <si>
     <t>1513</t>
@@ -1005,7 +1002,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1338,7 +1335,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>61</v>
@@ -1346,7 +1343,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>62</v>
@@ -1354,7 +1351,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>63</v>
@@ -1362,7 +1359,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>64</v>
@@ -1370,7 +1367,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>65</v>
@@ -1378,7 +1375,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>66</v>
@@ -1386,7 +1383,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>67</v>
@@ -1394,7 +1391,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>73</v>
@@ -1402,7 +1399,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>74</v>
@@ -1410,7 +1407,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>81</v>
@@ -1418,7 +1415,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>82</v>
@@ -1458,58 +1455,58 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23CC36F-B4BF-409B-B35F-BD2D71A00FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77FD8BD-7517-4618-BDDA-C8BEEDC5FE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="111">
   <si>
     <t>UA名字</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>2126</t>
+  </si>
+  <si>
+    <t>6485</t>
   </si>
 </sst>
 </file>
@@ -727,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B98"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -926,11 +929,11 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>17</v>
+      <c r="A25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -938,7 +941,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -946,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -954,7 +957,7 @@
         <v>1</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -962,7 +965,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -970,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -978,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -986,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -994,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1002,15 +1005,15 @@
         <v>1</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1018,7 +1021,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1026,7 +1029,7 @@
         <v>22</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1034,7 +1037,7 @@
         <v>22</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1042,7 +1045,7 @@
         <v>22</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1050,7 +1053,7 @@
         <v>22</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1058,7 +1061,7 @@
         <v>22</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1066,7 +1069,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1074,15 +1077,15 @@
         <v>22</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1090,7 +1093,7 @@
         <v>30</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1098,7 +1101,7 @@
         <v>30</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1106,7 +1109,7 @@
         <v>30</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1114,7 +1117,7 @@
         <v>30</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1122,15 +1125,15 @@
         <v>30</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1138,7 +1141,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1146,7 +1149,7 @@
         <v>37</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1154,7 +1157,7 @@
         <v>37</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1162,7 +1165,7 @@
         <v>37</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1170,7 +1173,7 @@
         <v>37</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1178,7 +1181,7 @@
         <v>37</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1186,7 +1189,7 @@
         <v>37</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1194,7 +1197,7 @@
         <v>37</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -1202,7 +1205,7 @@
         <v>37</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -1210,15 +1213,15 @@
         <v>37</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -1226,7 +1229,7 @@
         <v>47</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -1234,7 +1237,7 @@
         <v>47</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -1242,7 +1245,7 @@
         <v>47</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -1250,7 +1253,7 @@
         <v>47</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -1258,7 +1261,7 @@
         <v>47</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -1266,7 +1269,7 @@
         <v>47</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -1274,7 +1277,7 @@
         <v>47</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -1282,15 +1285,15 @@
         <v>47</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -1298,7 +1301,7 @@
         <v>97</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -1306,7 +1309,7 @@
         <v>97</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -1314,7 +1317,7 @@
         <v>97</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -1322,7 +1325,7 @@
         <v>97</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -1330,15 +1333,15 @@
         <v>97</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -1346,7 +1349,7 @@
         <v>104</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -1354,7 +1357,7 @@
         <v>104</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -1362,7 +1365,7 @@
         <v>104</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -1370,7 +1373,7 @@
         <v>104</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -1378,7 +1381,7 @@
         <v>104</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -1386,7 +1389,7 @@
         <v>104</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -1394,7 +1397,7 @@
         <v>104</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -1402,15 +1405,15 @@
         <v>104</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -1418,15 +1421,15 @@
         <v>104</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -1434,7 +1437,7 @@
         <v>68</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -1442,7 +1445,7 @@
         <v>68</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -1450,15 +1453,15 @@
         <v>68</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -1466,23 +1469,23 @@
         <v>108</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>109</v>
+      <c r="B93" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -1490,7 +1493,7 @@
         <v>100</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -1498,14 +1501,22 @@
         <v>100</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B98" s="3" t="s">
         <v>107</v>
       </c>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77FD8BD-7517-4618-BDDA-C8BEEDC5FE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2806F634-A31A-47A6-8802-7701BFCD80A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="112">
   <si>
     <t>UA名字</t>
   </si>
@@ -368,6 +368,10 @@
   </si>
   <si>
     <t>6485</t>
+  </si>
+  <si>
+    <t>0689</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -730,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -933,15 +937,15 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -949,7 +953,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -957,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -965,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -973,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -981,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -989,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -997,7 +1001,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1005,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1013,15 +1017,15 @@
         <v>1</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1029,7 +1033,7 @@
         <v>22</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1037,7 +1041,7 @@
         <v>22</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1045,7 +1049,7 @@
         <v>22</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1053,7 +1057,7 @@
         <v>22</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1061,7 +1065,7 @@
         <v>22</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1069,7 +1073,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1077,7 +1081,7 @@
         <v>22</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1085,15 +1089,15 @@
         <v>22</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1101,7 +1105,7 @@
         <v>30</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1109,7 +1113,7 @@
         <v>30</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1117,7 +1121,7 @@
         <v>30</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1125,7 +1129,7 @@
         <v>30</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1133,15 +1137,15 @@
         <v>30</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1149,7 +1153,7 @@
         <v>37</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1157,7 +1161,7 @@
         <v>37</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1165,7 +1169,7 @@
         <v>37</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1173,7 +1177,7 @@
         <v>37</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1181,7 +1185,7 @@
         <v>37</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1189,7 +1193,7 @@
         <v>37</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1197,7 +1201,7 @@
         <v>37</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -1205,7 +1209,7 @@
         <v>37</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -1213,7 +1217,7 @@
         <v>37</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -1221,15 +1225,15 @@
         <v>37</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -1237,7 +1241,7 @@
         <v>47</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -1245,7 +1249,7 @@
         <v>47</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -1253,7 +1257,7 @@
         <v>47</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -1261,7 +1265,7 @@
         <v>47</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -1269,7 +1273,7 @@
         <v>47</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -1277,7 +1281,7 @@
         <v>47</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -1285,7 +1289,7 @@
         <v>47</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -1293,15 +1297,15 @@
         <v>47</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -1309,7 +1313,7 @@
         <v>97</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -1317,7 +1321,7 @@
         <v>97</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -1325,7 +1329,7 @@
         <v>97</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -1333,7 +1337,7 @@
         <v>97</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -1341,15 +1345,15 @@
         <v>97</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -1357,7 +1361,7 @@
         <v>104</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -1365,7 +1369,7 @@
         <v>104</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -1373,7 +1377,7 @@
         <v>104</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -1381,7 +1385,7 @@
         <v>104</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -1389,7 +1393,7 @@
         <v>104</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -1397,7 +1401,7 @@
         <v>104</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -1405,7 +1409,7 @@
         <v>104</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -1413,15 +1417,15 @@
         <v>104</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -1429,15 +1433,15 @@
         <v>104</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -1445,7 +1449,7 @@
         <v>68</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -1453,7 +1457,7 @@
         <v>68</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -1461,15 +1465,15 @@
         <v>68</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -1477,23 +1481,23 @@
         <v>108</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>109</v>
+      <c r="B94" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -1501,7 +1505,7 @@
         <v>100</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -1509,14 +1513,22 @@
         <v>100</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B99" s="3" t="s">
         <v>107</v>
       </c>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2806F634-A31A-47A6-8802-7701BFCD80A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF074B3-9F16-4769-878F-EF63CC7E38B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF074B3-9F16-4769-878F-EF63CC7E38B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B679D79-07A1-406D-9049-0B2CB45FD63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21105" yWindow="1860" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="118">
   <si>
     <t>UA名字</t>
   </si>
@@ -371,7 +371,24 @@
   </si>
   <si>
     <t>0689</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5631</t>
+  </si>
+  <si>
+    <t>5066</t>
+  </si>
+  <si>
+    <t>wxh</t>
+  </si>
+  <si>
+    <t>3633</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>2281</t>
   </si>
 </sst>
 </file>
@@ -734,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -941,10 +958,10 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1530,6 +1547,38 @@
       </c>
       <c r="B99" s="3" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B679D79-07A1-406D-9049-0B2CB45FD63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C547F526-607D-4774-ABE3-CC438A84E453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21105" yWindow="1860" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="119">
   <si>
     <t>UA名字</t>
   </si>
@@ -389,6 +389,10 @@
   </si>
   <si>
     <t>2281</t>
+  </si>
+  <si>
+    <t>8565</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -751,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1581,6 +1585,14 @@
         <v>117</v>
       </c>
     </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C547F526-607D-4774-ABE3-CC438A84E453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55B4ADB-31D4-4364-9C97-9869BCE44FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21105" yWindow="1860" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="122">
   <si>
     <t>UA名字</t>
   </si>
@@ -392,7 +392,15 @@
   </si>
   <si>
     <t>8565</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1273</t>
+  </si>
+  <si>
+    <t>xxy</t>
+  </si>
+  <si>
+    <t>9299</t>
   </si>
 </sst>
 </file>
@@ -755,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1593,6 +1601,22 @@
         <v>118</v>
       </c>
     </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55B4ADB-31D4-4364-9C97-9869BCE44FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86664C0C-5554-481A-BE99-D1F180E82D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
   <si>
     <t>UA名字</t>
   </si>
@@ -401,6 +401,36 @@
   </si>
   <si>
     <t>9299</t>
+  </si>
+  <si>
+    <t>4439</t>
+  </si>
+  <si>
+    <t>4781</t>
+  </si>
+  <si>
+    <t>8775</t>
+  </si>
+  <si>
+    <t>4501</t>
+  </si>
+  <si>
+    <t>5252</t>
+  </si>
+  <si>
+    <t>8854</t>
+  </si>
+  <si>
+    <t>zm</t>
+  </si>
+  <si>
+    <t>7145</t>
+  </si>
+  <si>
+    <t>8935</t>
+  </si>
+  <si>
+    <t>9515</t>
   </si>
 </sst>
 </file>
@@ -763,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1474,11 +1504,11 @@
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>69</v>
+      <c r="A89" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -1486,7 +1516,7 @@
         <v>68</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -1494,7 +1524,7 @@
         <v>68</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -1502,47 +1532,47 @@
         <v>68</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>109</v>
+      <c r="B95" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -1550,71 +1580,163 @@
         <v>100</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>119</v>
+        <v>1</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86664C0C-5554-481A-BE99-D1F180E82D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0883CFCC-62C6-4785-A079-630B5FFBD343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="134">
   <si>
     <t>UA名字</t>
   </si>
@@ -42,10 +42,6 @@
     <t>mia</t>
   </si>
   <si>
-    <t>卡号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>willa</t>
   </si>
   <si>
@@ -431,6 +427,15 @@
   </si>
   <si>
     <t>9515</t>
+  </si>
+  <si>
+    <t>尾号</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>5643</t>
   </si>
 </sst>
 </file>
@@ -504,13 +509,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -793,951 +801,1087 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:C120"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" s="4"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="4"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="4"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="4"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="4"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" s="4"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="4"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="4"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" s="4"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="4"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="4"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" s="4"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="4"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" s="4"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C63" s="4"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="4"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C65" s="4"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" s="4"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C67" s="4"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" s="4"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="4"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C70" s="4"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71" s="4"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72" s="4"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C73" s="4"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" s="4"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="4"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="4"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C77" s="4"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="B78" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="4"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C79" s="4"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C80" s="4"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C81" s="4"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C82" s="4"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C83" s="4"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C84" s="4"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C85" s="4"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C86" s="4"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C87" s="4"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" s="4"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C89" s="4"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C90" s="4"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C91" s="4"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C92" s="4"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C93" s="4"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C94" s="4"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="C95" s="4"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C96" s="4"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C97" s="4"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C98" s="4"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C99" s="4"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+      <c r="C100" s="4"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B96" s="1" t="s">
+      <c r="C101" s="4"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B100" s="3" t="s">
+      <c r="B102" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C102" s="4"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
+      <c r="B103" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C103" s="4"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="C104" s="4"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C105" s="4"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
+      <c r="B106" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="C106" s="4"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
+      <c r="B107" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="C107" s="4"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B108" s="3" t="s">
+      <c r="C108" s="4"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="4"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C110" s="4"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="C111" s="4"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C112" s="4"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="4"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C114" s="4"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C115" s="4"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C116" s="4"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C117" s="4"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1" t="s">
-        <v>131</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C118" s="4"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C119" s="4"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C120" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0883CFCC-62C6-4785-A079-630B5FFBD343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077456A8-2164-4892-B4B9-99A4137C6EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077456A8-2164-4892-B4B9-99A4137C6EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68565F14-F62C-4326-89B1-8C9E89317E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
   <si>
     <t>UA名字</t>
   </si>
@@ -414,9 +414,6 @@
     <t>5252</t>
   </si>
   <si>
-    <t>8854</t>
-  </si>
-  <si>
     <t>zm</t>
   </si>
   <si>
@@ -424,9 +421,6 @@
   </si>
   <si>
     <t>8935</t>
-  </si>
-  <si>
-    <t>9515</t>
   </si>
   <si>
     <t>尾号</t>
@@ -812,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C1" s="4"/>
     </row>
@@ -1646,7 +1640,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>122</v>
@@ -1807,15 +1801,17 @@
       <c r="C111" s="4"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="1"/>
+      <c r="A112" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="B112" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C112" s="4"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>128</v>
@@ -1824,28 +1820,28 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C114" s="4"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C115" s="4"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C116" s="4"/>
     </row>
@@ -1854,33 +1850,23 @@
         <v>99</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C117" s="4"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
-      <c r="B118" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="B118" s="1"/>
       <c r="C118" s="4"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
       <c r="C119" s="4"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>133</v>
-      </c>
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
       <c r="C120" s="4"/>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68565F14-F62C-4326-89B1-8C9E89317E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357161A4-58B4-4384-A629-1A8DBA2281D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -423,13 +423,14 @@
     <t>8935</t>
   </si>
   <si>
-    <t>尾号</t>
-  </si>
-  <si>
     <t>1085</t>
   </si>
   <si>
     <t>5643</t>
+  </si>
+  <si>
+    <t>卡号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -806,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C1" s="4"/>
     </row>
@@ -1841,7 +1842,7 @@
         <v>119</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C116" s="4"/>
     </row>
@@ -1850,7 +1851,7 @@
         <v>99</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C117" s="4"/>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357161A4-58B4-4384-A629-1A8DBA2281D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14B3F0C-A356-4AF9-9B5F-1DE3A40AF5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="133">
   <si>
     <t>UA名字</t>
   </si>
@@ -431,6 +431,9 @@
   <si>
     <t>卡号</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4510</t>
   </si>
 </sst>
 </file>
@@ -1856,8 +1859,12 @@
       <c r="C117" s="4"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
+      <c r="A118" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="C118" s="4"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14B3F0C-A356-4AF9-9B5F-1DE3A40AF5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF8E1ED-E515-44DE-98A8-DAB9F3C35826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="134">
   <si>
     <t>UA名字</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t>4510</t>
+  </si>
+  <si>
+    <t>7474</t>
   </si>
 </sst>
 </file>
@@ -1868,8 +1871,12 @@
       <c r="C118" s="4"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
+      <c r="A119" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="C119" s="4"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF8E1ED-E515-44DE-98A8-DAB9F3C35826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6325C656-4884-400D-BBC6-72AF3C9DB497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="135">
   <si>
     <t>UA名字</t>
   </si>
@@ -437,6 +437,9 @@
   </si>
   <si>
     <t>7474</t>
+  </si>
+  <si>
+    <t>0956</t>
   </si>
 </sst>
 </file>
@@ -1880,8 +1883,12 @@
       <c r="C119" s="4"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
+      <c r="A120" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="C120" s="4"/>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6325C656-4884-400D-BBC6-72AF3C9DB497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7EDD98-0440-466C-87AC-928E96ED3434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="136">
   <si>
     <t>UA名字</t>
   </si>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t>0956</t>
+  </si>
+  <si>
+    <t>8854</t>
   </si>
 </sst>
 </file>
@@ -805,7 +808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C120"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1891,6 +1894,14 @@
       </c>
       <c r="C120" s="4"/>
     </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7EDD98-0440-466C-87AC-928E96ED3434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F076A785-4A9B-4E90-8467-86222ECAB0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="137">
   <si>
     <t>UA名字</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t>8854</t>
+  </si>
+  <si>
+    <t>5950</t>
   </si>
 </sst>
 </file>
@@ -808,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1902,6 +1905,14 @@
         <v>135</v>
       </c>
     </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F076A785-4A9B-4E90-8467-86222ECAB0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FE5FA5-18C9-4B60-A30C-4882E35706AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="138">
   <si>
     <t>UA名字</t>
   </si>
@@ -446,6 +446,9 @@
   </si>
   <si>
     <t>5950</t>
+  </si>
+  <si>
+    <t>2035</t>
   </si>
 </sst>
 </file>
@@ -811,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1913,6 +1916,14 @@
         <v>136</v>
       </c>
     </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FE5FA5-18C9-4B60-A30C-4882E35706AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A34142-A989-417D-82ED-2503139BCB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="139">
   <si>
     <t>UA名字</t>
   </si>
@@ -449,6 +449,9 @@
   </si>
   <si>
     <t>2035</t>
+  </si>
+  <si>
+    <t>4358</t>
   </si>
 </sst>
 </file>
@@ -814,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1740,55 +1743,55 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="C103" s="4"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C104" s="4"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C105" s="4"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C106" s="4"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C107" s="4"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C108" s="4"/>
     </row>
@@ -1796,53 +1799,53 @@
       <c r="A109" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>118</v>
+      <c r="B109" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="C109" s="4"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C110" s="4"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C111" s="4"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C112" s="4"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C113" s="4"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C114" s="4"/>
     </row>
@@ -1851,76 +1854,84 @@
         <v>99</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C115" s="4"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C116" s="4"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C117" s="4"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C118" s="4"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C119" s="4"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C120" s="4"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>137</v>
       </c>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A34142-A989-417D-82ED-2503139BCB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6D78B1-5BC0-4A8D-90E7-5EBEE2EB4687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="140">
   <si>
     <t>UA名字</t>
   </si>
@@ -452,6 +452,9 @@
   </si>
   <si>
     <t>4358</t>
+  </si>
+  <si>
+    <t>6516</t>
   </si>
 </sst>
 </file>
@@ -817,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C125"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1935,6 +1938,14 @@
         <v>137</v>
       </c>
     </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6D78B1-5BC0-4A8D-90E7-5EBEE2EB4687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE8CC60-9F8A-493B-AD55-BC03641A6E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="141">
   <si>
     <t>UA名字</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>6516</t>
+  </si>
+  <si>
+    <t>4170</t>
   </si>
 </sst>
 </file>
@@ -820,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1946,6 +1949,14 @@
         <v>139</v>
       </c>
     </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE8CC60-9F8A-493B-AD55-BC03641A6E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB4CC8C-4EA6-493D-B666-C7F766A0172B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="142">
   <si>
     <t>UA名字</t>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t>4170</t>
+  </si>
+  <si>
+    <t>4899</t>
   </si>
 </sst>
 </file>
@@ -823,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:C127"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1957,6 +1960,14 @@
         <v>140</v>
       </c>
     </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB4CC8C-4EA6-493D-B666-C7F766A0172B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFD685C-3C60-43D2-A95F-16544268E3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="143">
   <si>
     <t>UA名字</t>
   </si>
@@ -461,6 +461,9 @@
   </si>
   <si>
     <t>4899</t>
+  </si>
+  <si>
+    <t>6239</t>
   </si>
 </sst>
 </file>
@@ -826,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C128"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1968,6 +1971,14 @@
         <v>141</v>
       </c>
     </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFD685C-3C60-43D2-A95F-16544268E3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE5AC13-36A8-455B-9E4B-C46E04013B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="144">
   <si>
     <t>UA名字</t>
   </si>
@@ -464,6 +464,9 @@
   </si>
   <si>
     <t>6239</t>
+  </si>
+  <si>
+    <t>4924</t>
   </si>
 </sst>
 </file>
@@ -829,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C128"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1979,6 +1982,14 @@
         <v>142</v>
       </c>
     </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE5AC13-36A8-455B-9E4B-C46E04013B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E304E0-62CB-4988-AB47-DADF8AE619A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="146">
   <si>
     <t>UA名字</t>
   </si>
@@ -467,6 +467,14 @@
   </si>
   <si>
     <t>4924</t>
+  </si>
+  <si>
+    <t>zm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4069</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -832,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -1990,6 +1998,14 @@
         <v>143</v>
       </c>
     </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E304E0-62CB-4988-AB47-DADF8AE619A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A58A80-B1B0-4C48-875B-CD16D530259E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="147">
   <si>
     <t>UA名字</t>
   </si>
@@ -475,6 +475,9 @@
   <si>
     <t>4069</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3532</t>
   </si>
 </sst>
 </file>
@@ -840,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -2006,6 +2009,14 @@
         <v>145</v>
       </c>
     </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A58A80-B1B0-4C48-875B-CD16D530259E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68487328-52DB-4092-8B17-C14741EE5D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="148">
   <si>
     <t>UA名字</t>
   </si>
@@ -478,6 +478,9 @@
   </si>
   <si>
     <t>3532</t>
+  </si>
+  <si>
+    <t>9790</t>
   </si>
 </sst>
 </file>
@@ -843,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C132"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -2017,6 +2020,14 @@
         <v>146</v>
       </c>
     </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68487328-52DB-4092-8B17-C14741EE5D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919F190E-3016-4909-BAF1-ACA81879C9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="150">
   <si>
     <t>UA名字</t>
   </si>
@@ -481,6 +481,14 @@
   </si>
   <si>
     <t>9790</t>
+  </si>
+  <si>
+    <t>pan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1997</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -846,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -2028,6 +2036,14 @@
         <v>147</v>
       </c>
     </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919F190E-3016-4909-BAF1-ACA81879C9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8A477A-58A9-4E0D-ACAF-A6594630757D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="152">
   <si>
     <t>UA名字</t>
   </si>
@@ -488,6 +488,14 @@
   </si>
   <si>
     <t>1997</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6359</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -854,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -2044,6 +2052,14 @@
         <v>149</v>
       </c>
     </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
